--- a/sampleprojects/CorporateTax/excel/states/CA_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/CA_corp.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>DT: Determine CA Filing Requirement</t>
   </si>
@@ -143,13 +143,13 @@
     <t>Calculate CA income tax at 8.84% with $800 minimum; // Calculate CA income tax at 8.84%, enforce $800 minimum; set apportionment.state_tax = max(result.ca_minimum_franchise_tax, apportionment.state_taxable_income * apportionment.state_tax_rate - apportionment.state_credits); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
-    <t>if apportionment.state_taxable_income * apportionment.state_tax_rate - apportionment.state_credits &gt; result.ca_minimum_franchise_tax then set apportionment.state_tax = apportionment.state_taxable_income * apportionment.state_tax_rate - apportionment.state_credits; else set apportionment.state_tax = result.ca_minimum_franchise_tax; endif set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>if apportionment.state_taxable_income * ca_apportionment.state_tax_rate - apportionment.state_credits &gt; ca_result.minimum_franchise_tax then set apportionment.state_tax = apportionment.state_taxable_income * ca_apportionment.state_tax_rate - apportionment.state_credits; else set apportionment.state_tax = ca_result.minimum_franchise_tax; endif set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>No income but still owe minimum franchise tax; // No CA taxable income, but $800 minimum franchise tax still applies; set apportionment.state_tax = result.ca_minimum_franchise_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = result.ca_minimum_franchise_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set apportionment.state_tax = ca_result.minimum_franchise_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>No CA nexus - no tax or minimum franchise tax; // No CA nexus - no tax or minimum franchise tax; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
@@ -167,13 +167,13 @@
     <t>Has elected water's edge treatment</t>
   </si>
   <si>
-    <t>result.ca_waters_edge_election is true</t>
+    <t>ca_result.waters_edge_election is true</t>
   </si>
   <si>
     <t>Has unitary group members</t>
   </si>
   <si>
-    <t>result.ca_unitary_group_count &gt; 1</t>
+    <t>ca_result.unitary_group_count &gt; 1</t>
   </si>
   <si>
     <t>Water's edge limits combined reporting</t>
@@ -233,10 +233,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>ca_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -266,70 +266,40 @@
     <t>CA economic nexus threshold (2025: $610,395, indexed annually)</t>
   </si>
   <si>
-    <t>state_additions</t>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.0884</t>
+  </si>
+  <si>
+    <t>CA corporate tax rate: 8.84% (flat rate)</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>CA has no transaction count threshold (sales threshold only)</t>
+  </si>
+  <si>
+    <t>ca_result</t>
+  </si>
+  <si>
+    <t>enterprise_zone_credit</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>CA additions: federal interest, IRC 199A addback, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>California state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>CA credits: R&amp;D, hiring, film, etc.</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>CA subtractions: CA municipal interest, CA NOL, etc.</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>0.0884</t>
-  </si>
-  <si>
-    <t>CA corporate tax rate: 8.84% (flat rate)</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>CA has no transaction count threshold (sales threshold only)</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(4 attributes)</t>
-  </si>
-  <si>
-    <t>ca_enterprise_zone_credit</t>
-  </si>
-  <si>
     <t>CA enterprise zone hiring credit (legacy, being phased out)</t>
   </si>
   <si>
-    <t>ca_minimum_franchise_tax</t>
+    <t>minimum_franchise_tax</t>
   </si>
   <si>
     <t>800.0</t>
@@ -338,7 +308,7 @@
     <t>CA minimum franchise tax ($800 for most corporations)</t>
   </si>
   <si>
-    <t>ca_unitary_group_count</t>
+    <t>unitary_group_count</t>
   </si>
   <si>
     <t>1</t>
@@ -347,7 +317,7 @@
     <t>Number of corporations in CA unitary group (1 = standalone)</t>
   </si>
   <si>
-    <t>ca_waters_edge_election</t>
+    <t>waters_edge_election</t>
   </si>
   <si>
     <t>boolean</t>
@@ -3200,14 +3170,14 @@
       <c r="B7" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>74</v>
+      <c r="C7" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -3216,7 +3186,7 @@
         <v>76</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -3235,48 +3205,26 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -3285,299 +3233,157 @@
       <c r="C9" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>76</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>76</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>76</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="F12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H12" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M16" s="8" t="s">
+      <c r="I12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="8" t="s">
         <v>14</v>
       </c>
     </row>
